--- a/artfynd/A 60164-2024 artfynd.xlsx
+++ b/artfynd/A 60164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104000499</v>
+        <v>104000488</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545731.7151160532</v>
+        <v>545775</v>
       </c>
       <c r="R2" t="n">
-        <v>7121132.920526925</v>
+        <v>7121172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104000501</v>
+        <v>104000495</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tåsjöbergets sydbranter, Ång</t>
+          <t>Tåsjö sydbranter, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545777.6342545893</v>
+        <v>545631</v>
       </c>
       <c r="R3" t="n">
-        <v>7121212.431683142</v>
+        <v>7120971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104000266</v>
+        <v>104000499</v>
       </c>
       <c r="B4" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tåsjö sydbranter, Ång</t>
+          <t>Tåsjöbergets sydbranter, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545571.8078234175</v>
+        <v>545732</v>
       </c>
       <c r="R4" t="n">
-        <v>7120916.701913808</v>
+        <v>7121133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104000263</v>
+        <v>104000266</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2813</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545611.0796747993</v>
+        <v>545572</v>
       </c>
       <c r="R5" t="n">
-        <v>7120974.340069916</v>
+        <v>7120917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104000487</v>
+        <v>104000493</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545709.0069724054</v>
+        <v>545672</v>
       </c>
       <c r="R6" t="n">
-        <v>7121105.581065864</v>
+        <v>7121115</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104000497</v>
+        <v>104000492</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545728.5148569031</v>
+        <v>545663</v>
       </c>
       <c r="R7" t="n">
-        <v>7121142.890424676</v>
+        <v>7121109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104000505</v>
+        <v>104000494</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545702.0438821579</v>
+        <v>545685</v>
       </c>
       <c r="R8" t="n">
-        <v>7121104.606937774</v>
+        <v>7121125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,6 +1480,1055 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104000501</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545778</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7121212</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104000497</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>545729</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7121143</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104000486</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tåsjö sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545682</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7121039</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104000487</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545709</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7121105</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104000263</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tåsjö sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>545611</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7120974</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104000490</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tåsjö sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>545637</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7120969</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104000503</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>545732</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7121101</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104000257</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tåsjö sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>545590</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7120911</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104000489</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>545735</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7121101</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 60164-2024 artfynd.xlsx
+++ b/artfynd/A 60164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,48 +1951,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104000263</v>
+        <v>134787797</v>
       </c>
       <c r="B13" t="n">
-        <v>80468</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tåsjö sydbranter, Ång</t>
+          <t>Tåsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545611</v>
+        <v>545702</v>
       </c>
       <c r="R13" t="n">
-        <v>7120974</v>
+        <v>7121105</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,22 +2016,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,32 +2032,23 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104000490</v>
+        <v>104000263</v>
       </c>
       <c r="B14" t="n">
         <v>80468</v>
@@ -2102,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545637</v>
+        <v>545611</v>
       </c>
       <c r="R14" t="n">
-        <v>7120969</v>
+        <v>7120974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104000503</v>
+        <v>104000490</v>
       </c>
       <c r="B15" t="n">
         <v>80468</v>
@@ -2214,14 +2195,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tåsjöbergets sydbranter, Ång</t>
+          <t>Tåsjö sydbranter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545732</v>
+        <v>545637</v>
       </c>
       <c r="R15" t="n">
-        <v>7121101</v>
+        <v>7120969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104000257</v>
+        <v>104000503</v>
       </c>
       <c r="B16" t="n">
-        <v>101228</v>
+        <v>80468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,34 +2291,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tåsjö sydbranter, Ång</t>
+          <t>Tåsjöbergets sydbranter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545590</v>
+        <v>545732</v>
       </c>
       <c r="R16" t="n">
-        <v>7120911</v>
+        <v>7121101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2350,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2360,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104000489</v>
+        <v>134787800</v>
       </c>
       <c r="B17" t="n">
-        <v>80398</v>
+        <v>98219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2426,37 +2407,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229748</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tåsjöbergets sydbranter, Ång</t>
+          <t>Tåsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545735</v>
+        <v>545702</v>
       </c>
       <c r="R17" t="n">
-        <v>7121101</v>
+        <v>7121105</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,22 +2461,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,29 +2477,252 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104000257</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tåsjö sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>545590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7120911</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104000489</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tåsjöbergets sydbranter, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545735</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7121101</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 60164-2024 artfynd.xlsx
+++ b/artfynd/A 60164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000493</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000494</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000497</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000486</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000487</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787797</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000263</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000490</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2393,6 +2468,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000503</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2490,6 +2570,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787800</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2606,6 +2691,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000257</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2727,8 +2817,33 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>